--- a/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
+++ b/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\fuels\FoVTStCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\fuels\FoVTStCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5736511-220B-437D-B4AB-6A25C04B2BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EAC744-9BAA-497C-B24F-7F3CDDE3DD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="1140" windowWidth="23445" windowHeight="14565" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="9405" yWindow="810" windowWidth="19110" windowHeight="16425" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BFoVTStCT" sheetId="3" r:id="rId2"/>
+    <sheet name="FoVTStCT" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -673,32 +673,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE5FEEC-01CE-4291-999E-35B30A1256CF}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -715,14 +715,14 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="46.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -817,7 +817,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1419,7 +1419,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1451,7 +1451,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1483,7 +1483,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1515,7 +1515,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1547,7 +1547,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1579,7 +1579,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1611,7 +1611,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1643,7 +1643,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1675,7 +1675,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1707,7 +1707,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
     </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1739,7 +1739,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1771,7 +1771,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
     </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1803,7 +1803,7 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
     </row>
-    <row r="21" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1835,7 +1835,7 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
     </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1867,7 +1867,7 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
     </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1899,7 +1899,7 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
     </row>
-    <row r="24" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1931,7 +1931,7 @@
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
     </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1963,7 +1963,7 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
     </row>
-    <row r="26" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1995,7 +1995,7 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
     </row>
-    <row r="28" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
